--- a/java/mybatis/mybatis_javadoc_api.xlsx
+++ b/java/mybatis/mybatis_javadoc_api.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22368" windowHeight="9564" firstSheet="15" activeTab="22"/>
+    <workbookView windowWidth="21648" windowHeight="9155" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="org.apache.ibatis" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,455 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="490">
+  <si>
+    <t>Arg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a mapping definition for the constructor argument.</t>
+    </r>
+  </si>
+  <si>
+    <t>AutomapConstructor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The marker annotation that indicate a constructor for automatic mapping.</t>
+    </r>
+  </si>
+  <si>
+    <t>CacheNamespace</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify to use cache on namespace(e.g.</t>
+    </r>
+  </si>
+  <si>
+    <t>CacheNamespaceRef</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that reference a cache.</t>
+    </r>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>The annotation that conditional mapping definition for TypeDiscriminator.</t>
+  </si>
+  <si>
+    <t>ConstructorArgs</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that be grouping mapping definitions for constructor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify an SQL for deleting record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>Delete.List</t>
+  </si>
+  <si>
+    <t>The container annotation for Delete.</t>
+  </si>
+  <si>
+    <t>DeleteProvider</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a method that provide an SQL for deleting record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>DeleteProvider.List</t>
+  </si>
+  <si>
+    <t>The container annotation for DeleteProvider.</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The maker annotation that invoke a flush statements via Mapper interface.</t>
+    </r>
+  </si>
+  <si>
+    <t>Insert</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify an SQL for inserting record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>Insert.List</t>
+  </si>
+  <si>
+    <t>The container annotation for Insert.</t>
+  </si>
+  <si>
+    <t>InsertProvider</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a method that provide an SQL for inserting record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>InsertProvider.List</t>
+  </si>
+  <si>
+    <t>The container annotation for InsertProvider.</t>
+  </si>
+  <si>
+    <t>Lang</t>
+  </si>
+  <si>
+    <t>The annotation that specify a LanguageDriver to use.</t>
+  </si>
+  <si>
+    <t>Many</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify the nested statement for retrieving collections.</t>
+    </r>
+  </si>
+  <si>
+    <t>MapKey</t>
+  </si>
+  <si>
+    <t>The annotation that specify the property name(or column name) for a key value of Map.</t>
+  </si>
+  <si>
+    <t>Mapper</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Marker interface for MyBatis mappers.</t>
+    </r>
+  </si>
+  <si>
+    <t>One</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify the nested statement for retrieving single object.</t>
+    </r>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify options for customizing default behaviors.</t>
+    </r>
+  </si>
+  <si>
+    <t>Options.FlushCachePolicy</t>
+  </si>
+  <si>
+    <t>The options for the Options.flushCache().</t>
+  </si>
+  <si>
+    <t>Options.List</t>
+  </si>
+  <si>
+    <t>The container annotation for Options.</t>
+  </si>
+  <si>
+    <t>Param</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify the parameter name.</t>
+    </r>
+  </si>
+  <si>
+    <t>Property</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that inject a property value.</t>
+    </r>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a mapping definition for the property.</t>
+    </r>
+  </si>
+  <si>
+    <t>ResultMap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify result map names to use.</t>
+    </r>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that be grouping mapping definitions for property.</t>
+    </r>
+  </si>
+  <si>
+    <t>ResultType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>This annotation can be used when a @Select method is using a ResultHandler.</t>
+    </r>
+  </si>
+  <si>
+    <t>Select</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify an SQL for retrieving record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>Select.List</t>
+  </si>
+  <si>
+    <t>The container annotation for Select.</t>
+  </si>
+  <si>
+    <t>SelectKey</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify an SQL for retrieving a key value.</t>
+    </r>
+  </si>
+  <si>
+    <t>SelectKey.List</t>
+  </si>
+  <si>
+    <t>The container annotation for SelectKey.</t>
+  </si>
+  <si>
+    <t>SelectProvider</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a method that provide an SQL for retrieving record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>SelectProvider.List</t>
+  </si>
+  <si>
+    <t>The container annotation for SelectProvider.</t>
+  </si>
+  <si>
+    <t>TypeDiscriminator</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that be grouping conditional mapping definitions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify an SQL for updating record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>Update.List</t>
+  </si>
+  <si>
+    <t>The container annotation for Update.</t>
+  </si>
+  <si>
+    <t>UpdateProvider</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF474747"/>
+        <rFont val="Georgia"/>
+        <charset val="134"/>
+      </rPr>
+      <t>The annotation that specify a method that provide an SQL for updating record(s).</t>
+    </r>
+  </si>
+  <si>
+    <t>UpdateProvider.List</t>
+  </si>
+  <si>
+    <t>The container annotation for UpdateProvider.</t>
+  </si>
   <si>
     <t>BindingException</t>
   </si>
@@ -1172,9 +1620,6 @@
   </si>
   <si>
     <t>ResultFlag</t>
-  </si>
-  <si>
-    <t>ResultMap</t>
   </si>
   <si>
     <t>ResultMap.Builder</t>
@@ -3109,7 +3554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3132,6 +3577,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3472,7 +3920,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3480,7 +3928,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -3488,17 +3936,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" ht="57" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3506,7 +3954,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3514,7 +3962,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3522,7 +3970,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3530,7 +3978,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -3538,7 +3986,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -3546,7 +3994,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -3554,7 +4002,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -3562,17 +4010,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -3580,7 +4028,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -3588,7 +4036,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -3596,17 +4044,17 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" ht="19.2" spans="1:1">
       <c r="A44" s="4" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -3614,7 +4062,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -3622,27 +4070,27 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -3650,7 +4098,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -3658,7 +4106,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -3666,57 +4114,57 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" ht="19.2" spans="1:1">
       <c r="A81" s="4" t="s">
-        <v>105</v>
+        <v>185</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -3724,7 +4172,7 @@
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:1">
@@ -3732,7 +4180,7 @@
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
     </row>
     <row r="87" spans="1:1">
@@ -3740,17 +4188,17 @@
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -3758,7 +4206,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -3766,17 +4214,17 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" ht="19.2" spans="1:1">
       <c r="A99" s="4" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
     </row>
     <row r="101" spans="1:1">
@@ -3784,7 +4232,7 @@
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -3792,7 +4240,7 @@
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:1">
@@ -3800,7 +4248,7 @@
     </row>
     <row r="106" spans="1:1">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>198</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -3808,7 +4256,7 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>119</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -3816,7 +4264,7 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -3824,7 +4272,7 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3841,97 +4289,97 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" ht="138" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" ht="24" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="151.8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" ht="193.2" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" ht="151.8" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" ht="138" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" ht="248.4" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" ht="138" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -3939,12 +4387,12 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" ht="165.6" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3961,7 +4409,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3969,7 +4417,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -3977,7 +4425,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -3985,47 +4433,47 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" ht="69" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" ht="110.4" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" ht="138" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" ht="193.2" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" ht="24" spans="1:1">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -4033,22 +4481,22 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" ht="24" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -4071,22 +4519,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" ht="82.8" spans="1:1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" ht="27.6" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>156</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" ht="82.8" spans="1:1">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" ht="27.6" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -4106,7 +4554,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4114,7 +4562,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4122,17 +4570,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" ht="19.2" spans="1:1">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -4140,87 +4588,87 @@
     </row>
     <row r="14" ht="19.2" spans="1:1">
       <c r="A14" s="4" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" ht="19.2" spans="1:1">
       <c r="A28" s="4" t="s">
-        <v>175</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" ht="19.2" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" ht="19.2" spans="1:1">
       <c r="A36" s="4" t="s">
-        <v>179</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -4228,7 +4676,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>181</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -4236,37 +4684,37 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" ht="19.2" spans="1:1">
       <c r="A45" s="4" t="s">
-        <v>183</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" ht="19.2" spans="1:1">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" ht="19.2" spans="1:1">
       <c r="A58" s="4" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4286,17 +4734,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4304,27 +4752,27 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -4332,7 +4780,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -4340,7 +4788,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -4348,7 +4796,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -4356,7 +4804,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -4364,7 +4812,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -4372,7 +4820,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -4380,7 +4828,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -4388,7 +4836,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -4396,7 +4844,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -4404,7 +4852,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -4412,7 +4860,7 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -4420,7 +4868,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -4428,7 +4876,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>208</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -4436,7 +4884,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -4444,7 +4892,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -4452,7 +4900,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -4460,7 +4908,7 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -4468,7 +4916,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -4476,17 +4924,17 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>215</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -4494,12 +4942,12 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -4513,10 +4961,13 @@
   <sheetPr/>
   <dimension ref="A1:A11"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="26.6666666666667" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>219</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4524,7 +4975,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4532,7 +4983,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -4540,7 +4991,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4548,7 +4999,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -4556,7 +5007,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4576,7 +5027,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4584,7 +5035,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4592,17 +5043,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" ht="27.6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>228</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4610,7 +5061,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -4618,7 +5069,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -4626,12 +5077,12 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>233</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4651,17 +5102,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>234</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" ht="41.4" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>235</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>236</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4669,7 +5120,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -4677,17 +5128,17 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="27.6" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>239</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>240</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -4695,7 +5146,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -4703,22 +5154,22 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" ht="24" spans="1:1">
       <c r="A15" s="6" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>244</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -4726,7 +5177,7 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="1:1">
@@ -4734,7 +5185,7 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -4742,17 +5193,17 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" ht="82.8" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>248</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -4760,7 +5211,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -4768,7 +5219,7 @@
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>251</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -4776,12 +5227,12 @@
     </row>
     <row r="32" ht="19.2" spans="1:1">
       <c r="A32" s="4" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -4789,22 +5240,22 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" ht="41.4" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" ht="19.2" spans="1:1">
       <c r="A40" s="4" t="s">
-        <v>256</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>257</v>
+        <v>336</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -4812,7 +5263,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>258</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -4820,7 +5271,7 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>259</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -4828,7 +5279,7 @@
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>260</v>
+        <v>339</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -4836,7 +5287,7 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>261</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -4844,12 +5295,12 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="5" t="s">
-        <v>262</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>263</v>
+        <v>342</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -4857,7 +5308,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -4865,17 +5316,17 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>265</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" ht="19.2" spans="1:1">
       <c r="A62" s="4" t="s">
-        <v>266</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>267</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -4883,7 +5334,7 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -4891,7 +5342,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -4899,7 +5350,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -4907,7 +5358,7 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -4915,7 +5366,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -4923,7 +5374,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>273</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4943,7 +5394,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -4951,7 +5402,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4959,17 +5410,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" ht="19.2" spans="1:1">
       <c r="A9" s="4" t="s">
-        <v>277</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -4977,32 +5428,32 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21" ht="19.2" spans="1:1">
       <c r="A21" s="4" t="s">
-        <v>283</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>284</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -5010,7 +5461,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>285</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -5018,7 +5469,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>286</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -5026,7 +5477,7 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>287</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -5034,7 +5485,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>288</v>
+        <v>367</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -5042,7 +5493,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>289</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -5050,7 +5501,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>290</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -5058,27 +5509,27 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>291</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>292</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>293</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" ht="27.6" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>294</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>295</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -5086,7 +5537,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>296</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -5094,7 +5545,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>297</v>
+        <v>376</v>
       </c>
     </row>
     <row r="48" spans="1:1">
@@ -5102,7 +5553,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>298</v>
+        <v>377</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -5110,7 +5561,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>299</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -5118,7 +5569,7 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>300</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -5126,7 +5577,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>301</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -5134,7 +5585,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>302</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -5142,7 +5593,7 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:1">
@@ -5157,9 +5608,413 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A2:A81"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="48.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="82.8" spans="1:1">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="82.8" spans="1:1">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="55.2" spans="1:1">
+      <c r="A7" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="41.4" spans="1:1">
+      <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="69" spans="1:1">
+      <c r="A13" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="55.2" spans="1:1">
+      <c r="A15" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="82.8" spans="1:1">
+      <c r="A19" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="82.8" spans="1:1">
+      <c r="A23" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" ht="69" spans="1:1">
+      <c r="A25" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" ht="82.8" spans="1:1">
+      <c r="A29" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" ht="82.8" spans="1:1">
+      <c r="A35" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" ht="41.4" spans="1:1">
+      <c r="A39" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" ht="82.8" spans="1:1">
+      <c r="A41" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" ht="82.8" spans="1:1">
+      <c r="A43" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" ht="55.2" spans="1:1">
+      <c r="A49" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" ht="41.4" spans="1:1">
+      <c r="A51" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" ht="69" spans="1:1">
+      <c r="A53" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" ht="55.2" spans="1:1">
+      <c r="A55" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" ht="69" spans="1:1">
+      <c r="A57" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" ht="82.8" spans="1:1">
+      <c r="A59" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" ht="69" spans="1:1">
+      <c r="A61" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" ht="69" spans="1:1">
+      <c r="A65" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" ht="82.8" spans="1:1">
+      <c r="A69" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" ht="69" spans="1:1">
+      <c r="A73" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" ht="69" spans="1:1">
+      <c r="A75" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" ht="82.8" spans="1:1">
+      <c r="A79" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5176,27 +6031,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" ht="41.4" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>306</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" ht="55.2" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>307</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -5204,7 +6059,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>309</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -5212,7 +6067,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -5220,7 +6075,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -5228,7 +6083,7 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>312</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -5236,7 +6091,7 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -5244,7 +6099,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -5252,7 +6107,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>315</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -5260,17 +6115,17 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>316</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" ht="27.6" spans="1:1">
       <c r="A22" s="1" t="s">
-        <v>317</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>318</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" spans="1:1">
@@ -5278,27 +6133,27 @@
     </row>
     <row r="25" hidden="1" spans="1:1">
       <c r="A25" t="s">
-        <v>319</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" hidden="1" spans="1:1">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" hidden="1" spans="1:1">
       <c r="A27" t="s">
-        <v>321</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" hidden="1" spans="1:1">
       <c r="A28" t="s">
-        <v>322</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" hidden="1" spans="1:1">
       <c r="A29" t="s">
-        <v>323</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" hidden="1" spans="1:1">
@@ -5306,42 +6161,42 @@
     </row>
     <row r="31" hidden="1" spans="1:1">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" ht="19.2" spans="1:1">
       <c r="A34" s="4" t="s">
-        <v>325</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>327</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>328</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="6" t="s">
-        <v>329</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>330</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -5364,17 +6219,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>331</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -5382,62 +6237,62 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>335</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:1">
       <c r="A11" s="4" t="s">
-        <v>336</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="5" t="s">
-        <v>341</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>342</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>343</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>344</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>345</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -5457,17 +6312,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>346</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>347</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>348</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -5475,17 +6330,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>349</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>350</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>351</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -5493,7 +6348,7 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -5501,7 +6356,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -5509,17 +6364,17 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>355</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -5527,7 +6382,7 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>357</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -5535,7 +6390,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>358</v>
+        <v>437</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -5543,7 +6398,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>359</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -5551,7 +6406,7 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -5559,7 +6414,7 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -5567,17 +6422,17 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>362</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>363</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>364</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -5585,7 +6440,7 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>365</v>
+        <v>444</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -5593,7 +6448,7 @@
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>366</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -5601,7 +6456,7 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -5609,7 +6464,7 @@
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:1">
       <c r="A37" s="3" t="s">
-        <v>368</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -5617,7 +6472,7 @@
     </row>
     <row r="39" ht="35" customHeight="1" spans="1:1">
       <c r="A39" s="3" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -5625,7 +6480,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -5633,7 +6488,7 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -5641,7 +6496,7 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>372</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -5649,17 +6504,17 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>373</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>375</v>
+        <v>454</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -5667,7 +6522,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>376</v>
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -5675,7 +6530,7 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>377</v>
+        <v>456</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -5683,7 +6538,7 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -5691,7 +6546,7 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>379</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -5699,27 +6554,27 @@
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>380</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>381</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>382</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>383</v>
+        <v>462</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>384</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="1:1">
@@ -5727,7 +6582,7 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -5735,7 +6590,7 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>386</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -5743,7 +6598,7 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>387</v>
+        <v>466</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -5751,7 +6606,7 @@
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>388</v>
+        <v>467</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -5759,7 +6614,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -5767,7 +6622,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>390</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -5775,7 +6630,7 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>391</v>
+        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:1">
@@ -5783,7 +6638,7 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>392</v>
+        <v>471</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -5791,7 +6646,7 @@
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>393</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:1">
@@ -5799,7 +6654,7 @@
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>394</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -5807,17 +6662,17 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>395</v>
+        <v>474</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="1" t="s">
-        <v>396</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>397</v>
+        <v>476</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -5825,7 +6680,7 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="s">
-        <v>398</v>
+        <v>477</v>
       </c>
     </row>
     <row r="90" spans="1:1">
@@ -5833,7 +6688,7 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>399</v>
+        <v>478</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -5841,7 +6696,7 @@
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>400</v>
+        <v>479</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -5849,7 +6704,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>401</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -5857,7 +6712,7 @@
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="s">
-        <v>402</v>
+        <v>481</v>
       </c>
     </row>
     <row r="98" spans="1:1">
@@ -5865,17 +6720,17 @@
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>403</v>
+        <v>482</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>404</v>
+        <v>483</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>405</v>
+        <v>484</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -5883,17 +6738,17 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>406</v>
+        <v>485</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>407</v>
+        <v>486</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>408</v>
+        <v>487</v>
       </c>
     </row>
     <row r="106" spans="1:1">
@@ -5901,7 +6756,7 @@
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
     </row>
     <row r="108" spans="1:1">
@@ -5921,7 +6776,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>410</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -5941,32 +6796,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -5974,7 +6829,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -5982,7 +6837,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5999,7 +6854,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6007,7 +6862,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6015,27 +6870,27 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="82.8" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" ht="151.8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6055,7 +6910,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6063,7 +6918,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6071,7 +6926,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -6079,17 +6934,17 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="82.8" spans="1:1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" ht="27.6" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -6112,17 +6967,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" ht="55.2" spans="1:1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6130,7 +6985,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -6138,55 +6993,55 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" ht="24" spans="1:1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" ht="108" spans="1:1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="2"/>
     </row>
-    <row r="15" ht="57.6" spans="1:1">
+    <row r="15" ht="19.2" spans="1:1">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="55.2" spans="1:1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" ht="82.8" spans="1:1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -6194,17 +7049,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" ht="96.6" spans="1:1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -6212,7 +7067,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -6220,7 +7075,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -6228,17 +7083,17 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" ht="69" spans="1:1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -6246,32 +7101,32 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" ht="82.8" spans="1:1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" ht="69" spans="1:1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" ht="19.2" spans="1:1">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:1">
@@ -6294,32 +7149,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" ht="19.2" spans="1:1">
       <c r="A6" s="4" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="7" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" ht="27.6" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="25.2" spans="1:1">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -6346,7 +7201,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6354,57 +7209,57 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="19.2" spans="1:1">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" ht="41.4" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:1">
@@ -6412,7 +7267,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -6432,7 +7287,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6440,17 +7295,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" ht="24" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -6458,7 +7313,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:1">

--- a/java/mybatis/mybatis_javadoc_api.xlsx
+++ b/java/mybatis/mybatis_javadoc_api.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21648" windowHeight="9155" activeTab="1"/>
+    <workbookView windowWidth="22368" windowHeight="9564" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="org.apache.ibatis" sheetId="1" r:id="rId1"/>
@@ -3554,7 +3554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3577,9 +3577,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5619,8 +5616,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="82.8" spans="1:1">
-      <c r="A3" s="8" t="s">
+    <row r="3" ht="27.6" spans="1:1">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5629,8 +5626,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="82.8" spans="1:1">
-      <c r="A5" s="8" t="s">
+    <row r="5" ht="27.6" spans="1:1">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5639,8 +5636,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="55.2" spans="1:1">
-      <c r="A7" s="8" t="s">
+    <row r="7" ht="27.6" spans="1:1">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5649,8 +5646,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="41.4" spans="1:1">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5669,8 +5666,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="69" spans="1:1">
-      <c r="A13" s="8" t="s">
+    <row r="13" ht="27.6" spans="1:1">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5679,8 +5676,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" ht="55.2" spans="1:1">
-      <c r="A15" s="8" t="s">
+    <row r="15" ht="27.6" spans="1:1">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5699,8 +5696,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" ht="82.8" spans="1:1">
-      <c r="A19" s="8" t="s">
+    <row r="19" ht="27.6" spans="1:1">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5719,8 +5716,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="82.8" spans="1:1">
-      <c r="A23" s="8" t="s">
+    <row r="23" ht="27.6" spans="1:1">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5729,8 +5726,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" ht="69" spans="1:1">
-      <c r="A25" s="8" t="s">
+    <row r="25" ht="27.6" spans="1:1">
+      <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -5749,8 +5746,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" ht="82.8" spans="1:1">
-      <c r="A29" s="8" t="s">
+    <row r="29" ht="27.6" spans="1:1">
+      <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5779,8 +5776,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" ht="82.8" spans="1:1">
-      <c r="A35" s="8" t="s">
+    <row r="35" ht="27.6" spans="1:1">
+      <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5799,8 +5796,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" ht="41.4" spans="1:1">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5809,8 +5806,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" ht="82.8" spans="1:1">
-      <c r="A41" s="8" t="s">
+    <row r="41" ht="27.6" spans="1:1">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5819,8 +5816,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" ht="82.8" spans="1:1">
-      <c r="A43" s="8" t="s">
+    <row r="43" ht="27.6" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -5849,8 +5846,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" ht="55.2" spans="1:1">
-      <c r="A49" s="8" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5859,8 +5856,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" ht="41.4" spans="1:1">
-      <c r="A51" s="8" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5869,8 +5866,8 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" ht="69" spans="1:1">
-      <c r="A53" s="8" t="s">
+    <row r="53" ht="27.6" spans="1:1">
+      <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5879,8 +5876,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" ht="55.2" spans="1:1">
-      <c r="A55" s="8" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5889,8 +5886,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" ht="69" spans="1:1">
-      <c r="A57" s="8" t="s">
+    <row r="57" ht="27.6" spans="1:1">
+      <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5899,8 +5896,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" ht="82.8" spans="1:1">
-      <c r="A59" s="8" t="s">
+    <row r="59" ht="27.6" spans="1:1">
+      <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5909,8 +5906,8 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" ht="69" spans="1:1">
-      <c r="A61" s="8" t="s">
+    <row r="61" ht="27.6" spans="1:1">
+      <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5929,8 +5926,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" ht="69" spans="1:1">
-      <c r="A65" s="8" t="s">
+    <row r="65" ht="27.6" spans="1:1">
+      <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5949,8 +5946,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" ht="82.8" spans="1:1">
-      <c r="A69" s="8" t="s">
+    <row r="69" ht="27.6" spans="1:1">
+      <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5969,8 +5966,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" ht="69" spans="1:1">
-      <c r="A73" s="8" t="s">
+    <row r="73" ht="27.6" spans="1:1">
+      <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
@@ -5979,8 +5976,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" ht="69" spans="1:1">
-      <c r="A75" s="8" t="s">
+    <row r="75" ht="27.6" spans="1:1">
+      <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5999,8 +5996,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" ht="82.8" spans="1:1">
-      <c r="A79" s="8" t="s">
+    <row r="79" ht="27.6" spans="1:1">
+      <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
     </row>
